--- a/Team-Data/2014-15/1-10-2014-15.xlsx
+++ b/Team-Data/2014-15/1-10-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,19 +806,19 @@
         <v>5.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
         <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
         <v>15</v>
@@ -766,7 +833,7 @@
         <v>7</v>
       </c>
       <c r="AM2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN2" t="n">
         <v>4</v>
@@ -793,13 +860,13 @@
         <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW2" t="n">
         <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY2" t="n">
         <v>15</v>
@@ -811,7 +878,7 @@
         <v>9</v>
       </c>
       <c r="BB2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
         <v>6</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3" t="n">
         <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3" t="n">
-        <v>0.343</v>
+        <v>0.353</v>
       </c>
       <c r="H3" t="n">
         <v>48.7</v>
@@ -861,7 +928,7 @@
         <v>40.1</v>
       </c>
       <c r="J3" t="n">
-        <v>88.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K3" t="n">
         <v>0.453</v>
@@ -870,19 +937,19 @@
         <v>7.4</v>
       </c>
       <c r="M3" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="N3" t="n">
         <v>0.322</v>
       </c>
       <c r="O3" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="P3" t="n">
         <v>19.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.751</v>
+        <v>0.756</v>
       </c>
       <c r="R3" t="n">
         <v>10.5</v>
@@ -894,19 +961,19 @@
         <v>43.4</v>
       </c>
       <c r="U3" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="V3" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X3" t="n">
         <v>4.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z3" t="n">
         <v>21.7</v>
@@ -915,22 +982,22 @@
         <v>18.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>102.4</v>
+        <v>102.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.5</v>
+        <v>-1.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF3" t="n">
         <v>21</v>
       </c>
       <c r="AG3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH3" t="n">
         <v>4</v>
@@ -960,22 +1027,22 @@
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS3" t="n">
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
         <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AW3" t="n">
         <v>9</v>
@@ -993,10 +1060,10 @@
         <v>30</v>
       </c>
       <c r="BB3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E4" t="n">
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>0.432</v>
+        <v>0.444</v>
       </c>
       <c r="H4" t="n">
         <v>48.7</v>
@@ -1043,40 +1110,40 @@
         <v>36.1</v>
       </c>
       <c r="J4" t="n">
-        <v>81.2</v>
+        <v>81</v>
       </c>
       <c r="K4" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L4" t="n">
         <v>6.8</v>
       </c>
       <c r="M4" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0.323</v>
+        <v>0.324</v>
       </c>
       <c r="O4" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="P4" t="n">
-        <v>22.1</v>
+        <v>22.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.747</v>
+        <v>0.744</v>
       </c>
       <c r="R4" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="T4" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U4" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V4" t="n">
         <v>14.7</v>
@@ -1085,43 +1152,43 @@
         <v>7.1</v>
       </c>
       <c r="X4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z4" t="n">
         <v>20.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.3</v>
+        <v>20.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.2</v>
+        <v>-2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
       </c>
       <c r="AF4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG4" t="n">
         <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>25</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>24</v>
       </c>
       <c r="AK4" t="n">
         <v>19</v>
@@ -1130,7 +1197,7 @@
         <v>24</v>
       </c>
       <c r="AM4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AN4" t="n">
         <v>25</v>
@@ -1142,7 +1209,7 @@
         <v>21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR4" t="n">
         <v>26</v>
@@ -1151,28 +1218,28 @@
         <v>13</v>
       </c>
       <c r="AT4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AU4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AV4" t="n">
         <v>19</v>
       </c>
-      <c r="AV4" t="n">
-        <v>20</v>
-      </c>
       <c r="AW4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY4" t="n">
         <v>12</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BB4" t="n">
         <v>25</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
         <v>24</v>
       </c>
       <c r="G5" t="n">
-        <v>0.385</v>
+        <v>0.368</v>
       </c>
       <c r="H5" t="n">
         <v>48.8</v>
@@ -1225,76 +1292,76 @@
         <v>36.4</v>
       </c>
       <c r="J5" t="n">
-        <v>84.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.431</v>
+        <v>0.429</v>
       </c>
       <c r="L5" t="n">
         <v>5.9</v>
       </c>
       <c r="M5" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>0.313</v>
+        <v>0.31</v>
       </c>
       <c r="O5" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="P5" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="R5" t="n">
         <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>33.1</v>
+        <v>32.9</v>
       </c>
       <c r="T5" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="U5" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V5" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="W5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="X5" t="n">
         <v>4.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>96</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AF5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG5" t="n">
         <v>22</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>21</v>
       </c>
       <c r="AH5" t="n">
         <v>3</v>
@@ -1306,19 +1373,19 @@
         <v>11</v>
       </c>
       <c r="AK5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL5" t="n">
         <v>27</v>
       </c>
       <c r="AM5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AN5" t="n">
         <v>29</v>
       </c>
       <c r="AO5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP5" t="n">
         <v>16</v>
@@ -1327,13 +1394,13 @@
         <v>22</v>
       </c>
       <c r="AR5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU5" t="n">
         <v>25</v>
@@ -1348,7 +1415,7 @@
         <v>12</v>
       </c>
       <c r="AY5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ5" t="n">
         <v>4</v>
@@ -1357,10 +1424,10 @@
         <v>8</v>
       </c>
       <c r="BB5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
         <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.676</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
@@ -1407,19 +1474,19 @@
         <v>36.6</v>
       </c>
       <c r="J6" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L6" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M6" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="N6" t="n">
-        <v>0.356</v>
+        <v>0.359</v>
       </c>
       <c r="O6" t="n">
         <v>21.2</v>
@@ -1428,19 +1495,19 @@
         <v>27.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.78</v>
+        <v>0.778</v>
       </c>
       <c r="R6" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="S6" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="T6" t="n">
-        <v>46.1</v>
+        <v>45.9</v>
       </c>
       <c r="U6" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V6" t="n">
         <v>14.6</v>
@@ -1452,7 +1519,7 @@
         <v>6.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z6" t="n">
         <v>18.6</v>
@@ -1461,16 +1528,16 @@
         <v>22.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.7</v>
+        <v>101.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD6" t="n">
         <v>7</v>
       </c>
       <c r="AE6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF6" t="n">
         <v>9</v>
@@ -1479,10 +1546,10 @@
         <v>9</v>
       </c>
       <c r="AH6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AJ6" t="n">
         <v>19</v>
@@ -1494,10 +1561,10 @@
         <v>13</v>
       </c>
       <c r="AM6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1506,13 +1573,13 @@
         <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS6" t="n">
         <v>5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>6</v>
       </c>
       <c r="AT6" t="n">
         <v>3</v>
@@ -1521,7 +1588,7 @@
         <v>13</v>
       </c>
       <c r="AV6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW6" t="n">
         <v>28</v>
@@ -1539,7 +1606,7 @@
         <v>2</v>
       </c>
       <c r="BB6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>0.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE7" t="n">
         <v>14</v>
@@ -1658,16 +1725,16 @@
         <v>13</v>
       </c>
       <c r="AG7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
         <v>18</v>
       </c>
       <c r="AJ7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK7" t="n">
         <v>18</v>
@@ -1679,13 +1746,13 @@
         <v>12</v>
       </c>
       <c r="AN7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ7" t="n">
         <v>12</v>
@@ -1724,7 +1791,7 @@
         <v>17</v>
       </c>
       <c r="BC7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -1771,67 +1838,67 @@
         <v>41.1</v>
       </c>
       <c r="J8" t="n">
-        <v>86.5</v>
+        <v>86.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.475</v>
+        <v>0.476</v>
       </c>
       <c r="L8" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="M8" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0.361</v>
+        <v>0.36</v>
       </c>
       <c r="O8" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="P8" t="n">
         <v>22.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.76</v>
+        <v>0.763</v>
       </c>
       <c r="R8" t="n">
         <v>10.9</v>
       </c>
       <c r="S8" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="T8" t="n">
-        <v>42.4</v>
+        <v>42.2</v>
       </c>
       <c r="U8" t="n">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
       <c r="V8" t="n">
         <v>12.2</v>
       </c>
       <c r="W8" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y8" t="n">
         <v>3.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AB8" t="n">
         <v>109.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE8" t="n">
         <v>4</v>
@@ -1849,7 +1916,7 @@
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK8" t="n">
         <v>2</v>
@@ -1858,28 +1925,28 @@
         <v>6</v>
       </c>
       <c r="AM8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN8" t="n">
         <v>11</v>
       </c>
       <c r="AO8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP8" t="n">
         <v>17</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
         <v>16</v>
       </c>
       <c r="AS8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
@@ -1897,7 +1964,7 @@
         <v>2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
         <v>3</v>
@@ -1906,7 +1973,7 @@
         <v>2</v>
       </c>
       <c r="BC8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -2013,10 +2080,10 @@
         <v>-1.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF9" t="n">
         <v>17</v>
@@ -2031,10 +2098,10 @@
         <v>13</v>
       </c>
       <c r="AJ9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL9" t="n">
         <v>12</v>
@@ -2046,16 +2113,16 @@
         <v>26</v>
       </c>
       <c r="AO9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ9" t="n">
         <v>23</v>
       </c>
       <c r="AR9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS9" t="n">
         <v>8</v>
@@ -2076,7 +2143,7 @@
         <v>13</v>
       </c>
       <c r="AY9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ9" t="n">
         <v>30</v>
@@ -2085,10 +2152,10 @@
         <v>10</v>
       </c>
       <c r="BB9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -2117,61 +2184,61 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F10" t="n">
         <v>24</v>
       </c>
       <c r="G10" t="n">
-        <v>0.351</v>
+        <v>0.333</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J10" t="n">
-        <v>85.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K10" t="n">
         <v>0.426</v>
       </c>
       <c r="L10" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="M10" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="N10" t="n">
         <v>0.345</v>
       </c>
       <c r="O10" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="P10" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="S10" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="T10" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
       <c r="U10" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V10" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="W10" t="n">
         <v>7.6</v>
@@ -2180,34 +2247,34 @@
         <v>4.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB10" t="n">
         <v>97.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.2</v>
+        <v>-2.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF10" t="n">
         <v>23</v>
       </c>
-      <c r="AF10" t="n">
-        <v>22</v>
-      </c>
       <c r="AG10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI10" t="n">
         <v>19</v>
@@ -2225,13 +2292,13 @@
         <v>8</v>
       </c>
       <c r="AN10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
         <v>26</v>
       </c>
       <c r="AP10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ10" t="n">
         <v>29</v>
@@ -2240,13 +2307,13 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT10" t="n">
         <v>5</v>
       </c>
       <c r="AU10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV10" t="n">
         <v>8</v>
@@ -2255,7 +2322,7 @@
         <v>14</v>
       </c>
       <c r="AX10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY10" t="n">
         <v>16</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>11</v>
       </c>
       <c r="AD11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2395,7 +2462,7 @@
         <v>1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK11" t="n">
         <v>1</v>
@@ -2413,10 +2480,10 @@
         <v>21</v>
       </c>
       <c r="AP11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR11" t="n">
         <v>23</v>
@@ -2440,13 +2507,13 @@
         <v>2</v>
       </c>
       <c r="AY11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BB11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2566,7 @@
         <v>36.2</v>
       </c>
       <c r="J12" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="K12" t="n">
         <v>0.435</v>
@@ -2508,61 +2575,61 @@
         <v>11.8</v>
       </c>
       <c r="M12" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O12" t="n">
-        <v>17.1</v>
+        <v>17.6</v>
       </c>
       <c r="P12" t="n">
-        <v>24.2</v>
+        <v>25</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.707</v>
+        <v>0.702</v>
       </c>
       <c r="R12" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S12" t="n">
-        <v>31.4</v>
+        <v>31.6</v>
       </c>
       <c r="T12" t="n">
-        <v>43.8</v>
+        <v>44.2</v>
       </c>
       <c r="U12" t="n">
         <v>20.6</v>
       </c>
       <c r="V12" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="W12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="X12" t="n">
         <v>4.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.6</v>
+        <v>21</v>
       </c>
       <c r="AB12" t="n">
-        <v>101.3</v>
+        <v>101.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF12" t="n">
         <v>4</v>
@@ -2571,7 +2638,7 @@
         <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI12" t="n">
         <v>24</v>
@@ -2580,7 +2647,7 @@
         <v>16</v>
       </c>
       <c r="AK12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL12" t="n">
         <v>1</v>
@@ -2592,10 +2659,10 @@
         <v>17</v>
       </c>
       <c r="AO12" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AP12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
@@ -2604,10 +2671,10 @@
         <v>4</v>
       </c>
       <c r="AS12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AT12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU12" t="n">
         <v>23</v>
@@ -2622,16 +2689,16 @@
         <v>15</v>
       </c>
       <c r="AY12" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BB12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC12" t="n">
         <v>7</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -2663,58 +2730,58 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E13" t="n">
         <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>0.385</v>
+        <v>0.395</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>35.9</v>
+        <v>36.1</v>
       </c>
       <c r="J13" t="n">
         <v>84.09999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.427</v>
+        <v>0.43</v>
       </c>
       <c r="L13" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M13" t="n">
         <v>20.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.339</v>
+        <v>0.342</v>
       </c>
       <c r="O13" t="n">
-        <v>16.4</v>
+        <v>16.1</v>
       </c>
       <c r="P13" t="n">
-        <v>21.8</v>
+        <v>21.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.754</v>
+        <v>0.756</v>
       </c>
       <c r="R13" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="S13" t="n">
         <v>34.2</v>
       </c>
       <c r="T13" t="n">
-        <v>45.4</v>
+        <v>45.1</v>
       </c>
       <c r="U13" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V13" t="n">
         <v>14.3</v>
@@ -2726,22 +2793,22 @@
         <v>4.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>95.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC13" t="n">
         <v>-1.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE13" t="n">
         <v>19</v>
@@ -2756,34 +2823,34 @@
         <v>19</v>
       </c>
       <c r="AI13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK13" t="n">
         <v>27</v>
       </c>
-      <c r="AJ13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>28</v>
-      </c>
       <c r="AL13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AM13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AN13" t="n">
         <v>22</v>
       </c>
       <c r="AO13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP13" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS13" t="n">
         <v>4</v>
@@ -2792,7 +2859,7 @@
         <v>6</v>
       </c>
       <c r="AU13" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AV13" t="n">
         <v>11</v>
@@ -2804,19 +2871,19 @@
         <v>18</v>
       </c>
       <c r="AY13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ13" t="n">
         <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BB13" t="n">
         <v>26</v>
       </c>
       <c r="BC13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -2845,58 +2912,58 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>0.676</v>
+        <v>0.667</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
       <c r="J14" t="n">
-        <v>81.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="K14" t="n">
-        <v>0.474</v>
+        <v>0.472</v>
       </c>
       <c r="L14" t="n">
         <v>10.3</v>
       </c>
       <c r="M14" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0.385</v>
+        <v>0.384</v>
       </c>
       <c r="O14" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="P14" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.752</v>
+        <v>0.753</v>
       </c>
       <c r="R14" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>32.6</v>
+        <v>32.4</v>
       </c>
       <c r="T14" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="U14" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="V14" t="n">
         <v>12.5</v>
@@ -2911,22 +2978,22 @@
         <v>2.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.8</v>
+        <v>106.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AD14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE14" t="n">
         <v>9</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>6</v>
       </c>
       <c r="AF14" t="n">
         <v>9</v>
@@ -2938,13 +3005,13 @@
         <v>26</v>
       </c>
       <c r="AI14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AJ14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
         <v>2</v>
@@ -2956,13 +3023,13 @@
         <v>2</v>
       </c>
       <c r="AO14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP14" t="n">
         <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR14" t="n">
         <v>28</v>
@@ -2971,7 +3038,7 @@
         <v>14</v>
       </c>
       <c r="AT14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AU14" t="n">
         <v>5</v>
@@ -2983,7 +3050,7 @@
         <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -2998,7 +3065,7 @@
         <v>5</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E15" t="n">
         <v>12</v>
       </c>
       <c r="F15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G15" t="n">
-        <v>0.333</v>
+        <v>0.324</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>38.2</v>
+        <v>37.9</v>
       </c>
       <c r="J15" t="n">
-        <v>86.7</v>
+        <v>86.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.44</v>
+        <v>0.438</v>
       </c>
       <c r="L15" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M15" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="O15" t="n">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="P15" t="n">
-        <v>24.8</v>
+        <v>25.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.744</v>
+        <v>0.747</v>
       </c>
       <c r="R15" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S15" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="T15" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="U15" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V15" t="n">
         <v>12.5</v>
@@ -3090,94 +3157,94 @@
         <v>4.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>101.9</v>
+        <v>101.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.6</v>
+        <v>-5.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF15" t="n">
         <v>26</v>
       </c>
-      <c r="AF15" t="n">
-        <v>22</v>
-      </c>
       <c r="AG15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI15" t="n">
         <v>12</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AM15" t="n">
         <v>22</v>
       </c>
       <c r="AN15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP15" t="n">
         <v>7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AR15" t="n">
         <v>7</v>
       </c>
       <c r="AS15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV15" t="n">
         <v>4</v>
       </c>
       <c r="AW15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX15" t="n">
         <v>17</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>15</v>
       </c>
       <c r="AY15" t="n">
         <v>7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BB15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -3287,10 +3354,10 @@
         <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF16" t="n">
         <v>4</v>
@@ -3302,13 +3369,13 @@
         <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ16" t="n">
         <v>15</v>
       </c>
       <c r="AK16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL16" t="n">
         <v>28</v>
@@ -3317,7 +3384,7 @@
         <v>27</v>
       </c>
       <c r="AN16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO16" t="n">
         <v>9</v>
@@ -3332,7 +3399,7 @@
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT16" t="n">
         <v>20</v>
@@ -3350,13 +3417,13 @@
         <v>24</v>
       </c>
       <c r="AY16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BB16" t="n">
         <v>16</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -3469,13 +3536,13 @@
         <v>-4.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
       </c>
       <c r="AF17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG17" t="n">
         <v>19</v>
@@ -3505,10 +3572,10 @@
         <v>10</v>
       </c>
       <c r="AP17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3541,7 +3608,7 @@
         <v>14</v>
       </c>
       <c r="BB17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC17" t="n">
         <v>25</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -3573,19 +3640,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E18" t="n">
         <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>0.513</v>
+        <v>0.526</v>
       </c>
       <c r="H18" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I18" t="n">
         <v>37.8</v>
@@ -3597,43 +3664,43 @@
         <v>0.464</v>
       </c>
       <c r="L18" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M18" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.361</v>
+        <v>0.363</v>
       </c>
       <c r="O18" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P18" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Q18" t="n">
         <v>0.777</v>
       </c>
       <c r="R18" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S18" t="n">
-        <v>30.8</v>
+        <v>31</v>
       </c>
       <c r="T18" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U18" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="V18" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="W18" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Y18" t="n">
         <v>4.8</v>
@@ -3645,22 +3712,22 @@
         <v>19.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.5</v>
+        <v>98.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE18" t="n">
         <v>13</v>
       </c>
       <c r="AF18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH18" t="n">
         <v>8</v>
@@ -3672,19 +3739,19 @@
         <v>23</v>
       </c>
       <c r="AK18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM18" t="n">
         <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP18" t="n">
         <v>26</v>
@@ -3696,10 +3763,10 @@
         <v>22</v>
       </c>
       <c r="AS18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT18" t="n">
         <v>24</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>26</v>
       </c>
       <c r="AU18" t="n">
         <v>8</v>
@@ -3711,7 +3778,7 @@
         <v>3</v>
       </c>
       <c r="AX18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY18" t="n">
         <v>13</v>
@@ -3720,10 +3787,10 @@
         <v>27</v>
       </c>
       <c r="BA18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC18" t="n">
         <v>13</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -3755,61 +3822,61 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19" t="n">
         <v>5</v>
       </c>
       <c r="F19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G19" t="n">
-        <v>0.139</v>
+        <v>0.143</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
       </c>
       <c r="I19" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J19" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.435</v>
+        <v>0.436</v>
       </c>
       <c r="L19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
         <v>14.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.335</v>
+        <v>0.338</v>
       </c>
       <c r="O19" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="P19" t="n">
         <v>25.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.737</v>
+        <v>0.729</v>
       </c>
       <c r="R19" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="S19" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="T19" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U19" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="V19" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W19" t="n">
         <v>9.1</v>
@@ -3818,7 +3885,7 @@
         <v>4.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z19" t="n">
         <v>20.3</v>
@@ -3827,13 +3894,13 @@
         <v>22.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>98.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-10.1</v>
+        <v>-10</v>
       </c>
       <c r="AD19" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3845,7 +3912,7 @@
         <v>29</v>
       </c>
       <c r="AH19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
         <v>16</v>
@@ -3854,7 +3921,7 @@
         <v>8</v>
       </c>
       <c r="AK19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
         <v>30</v>
@@ -3866,16 +3933,16 @@
         <v>23</v>
       </c>
       <c r="AO19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AP19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AR19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS19" t="n">
         <v>29</v>
@@ -3887,13 +3954,13 @@
         <v>11</v>
       </c>
       <c r="AV19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW19" t="n">
         <v>5</v>
       </c>
       <c r="AX19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY19" t="n">
         <v>28</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F20" t="n">
         <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>0.486</v>
+        <v>0.5</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3955,88 +4022,88 @@
         <v>38.8</v>
       </c>
       <c r="J20" t="n">
-        <v>84.3</v>
+        <v>84.8</v>
       </c>
       <c r="K20" t="n">
-        <v>0.46</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M20" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0.345</v>
+        <v>0.342</v>
       </c>
       <c r="O20" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P20" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.765</v>
+        <v>0.755</v>
       </c>
       <c r="R20" t="n">
-        <v>11.3</v>
+        <v>11.7</v>
       </c>
       <c r="S20" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T20" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="U20" t="n">
         <v>21.4</v>
       </c>
       <c r="V20" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="W20" t="n">
         <v>7.4</v>
       </c>
       <c r="X20" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z20" t="n">
         <v>19.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="AB20" t="n">
         <v>101.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AE20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ20" t="n">
         <v>12</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
         <v>25</v>
@@ -4045,25 +4112,25 @@
         <v>23</v>
       </c>
       <c r="AN20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO20" t="n">
         <v>18</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AP20" t="n">
         <v>19</v>
       </c>
-      <c r="AP20" t="n">
-        <v>20</v>
-      </c>
       <c r="AQ20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT20" t="n">
         <v>11</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>14</v>
       </c>
       <c r="AU20" t="n">
         <v>14</v>
@@ -4072,25 +4139,25 @@
         <v>6</v>
       </c>
       <c r="AW20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ20" t="n">
         <v>6</v>
       </c>
       <c r="BA20" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BB20" t="n">
         <v>15</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -4119,64 +4186,64 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E21" t="n">
         <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G21" t="n">
-        <v>0.125</v>
+        <v>0.128</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J21" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K21" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L21" t="n">
         <v>7.3</v>
       </c>
       <c r="M21" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0.353</v>
+        <v>0.356</v>
       </c>
       <c r="O21" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="P21" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R21" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S21" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="T21" t="n">
-        <v>39.2</v>
+        <v>39.5</v>
       </c>
       <c r="U21" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V21" t="n">
         <v>15</v>
       </c>
       <c r="W21" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X21" t="n">
         <v>3.7</v>
@@ -4188,13 +4255,13 @@
         <v>22.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>92.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>-9</v>
+        <v>-8.5</v>
       </c>
       <c r="AD21" t="n">
         <v>1</v>
@@ -4215,7 +4282,7 @@
         <v>26</v>
       </c>
       <c r="AJ21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK21" t="n">
         <v>21</v>
@@ -4224,22 +4291,22 @@
         <v>16</v>
       </c>
       <c r="AM21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP21" t="n">
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
         <v>28</v>
@@ -4251,7 +4318,7 @@
         <v>15</v>
       </c>
       <c r="AV21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW21" t="n">
         <v>15</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -4379,16 +4446,16 @@
         <v>0.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
         <v>15</v>
       </c>
       <c r="AF22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH22" t="n">
         <v>16</v>
@@ -4397,13 +4464,13 @@
         <v>17</v>
       </c>
       <c r="AJ22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM22" t="n">
         <v>14</v>
@@ -4418,10 +4485,10 @@
         <v>12</v>
       </c>
       <c r="AQ22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AR22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS22" t="n">
         <v>3</v>
@@ -4439,19 +4506,19 @@
         <v>23</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
         <v>14</v>
       </c>
       <c r="AZ22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BB22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC22" t="n">
         <v>14</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -4498,22 +4565,22 @@
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>36.6</v>
+        <v>36.4</v>
       </c>
       <c r="J23" t="n">
-        <v>81</v>
+        <v>80.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L23" t="n">
         <v>7.1</v>
       </c>
       <c r="M23" t="n">
-        <v>19.2</v>
+        <v>18.9</v>
       </c>
       <c r="N23" t="n">
-        <v>0.368</v>
+        <v>0.374</v>
       </c>
       <c r="O23" t="n">
         <v>13.6</v>
@@ -4522,46 +4589,46 @@
         <v>18.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.727</v>
+        <v>0.728</v>
       </c>
       <c r="R23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="T23" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="U23" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V23" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W23" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X23" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA23" t="n">
         <v>18.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>93.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.5</v>
+        <v>-5.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>23</v>
@@ -4570,13 +4637,13 @@
         <v>27</v>
       </c>
       <c r="AG23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH23" t="n">
         <v>28</v>
       </c>
       <c r="AI23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ23" t="n">
         <v>26</v>
@@ -4585,16 +4652,16 @@
         <v>16</v>
       </c>
       <c r="AL23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AM23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AN23" t="n">
         <v>7</v>
       </c>
       <c r="AO23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP23" t="n">
         <v>29</v>
@@ -4612,19 +4679,19 @@
         <v>28</v>
       </c>
       <c r="AU23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AY23" t="n">
         <v>26</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>30</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>23</v>
       </c>
       <c r="AZ23" t="n">
         <v>18</v>
@@ -4633,7 +4700,7 @@
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
         <v>29</v>
       </c>
       <c r="G24" t="n">
-        <v>0.194</v>
+        <v>0.171</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
@@ -4689,13 +4756,13 @@
         <v>0.411</v>
       </c>
       <c r="L24" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M24" t="n">
         <v>23.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0.299</v>
+        <v>0.294</v>
       </c>
       <c r="O24" t="n">
         <v>16.8</v>
@@ -4704,7 +4771,7 @@
         <v>24.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.681</v>
+        <v>0.68</v>
       </c>
       <c r="R24" t="n">
         <v>11.6</v>
@@ -4713,37 +4780,37 @@
         <v>30.4</v>
       </c>
       <c r="T24" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U24" t="n">
         <v>19.9</v>
       </c>
       <c r="V24" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="W24" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="X24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y24" t="n">
         <v>5.7</v>
       </c>
-      <c r="Y24" t="n">
-        <v>5.6</v>
-      </c>
       <c r="Z24" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>90.59999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>-12.5</v>
+        <v>-12.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,19 +4822,19 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
       </c>
       <c r="AJ24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK24" t="n">
         <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AM24" t="n">
         <v>10</v>
@@ -4779,13 +4846,13 @@
         <v>20</v>
       </c>
       <c r="AP24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
         <v>25</v>
@@ -4794,7 +4861,7 @@
         <v>21</v>
       </c>
       <c r="AU24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4803,16 +4870,16 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY24" t="n">
         <v>25</v>
       </c>
       <c r="AZ24" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BA24" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>11</v>
@@ -4952,13 +5019,13 @@
         <v>5</v>
       </c>
       <c r="AM25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN25" t="n">
         <v>8</v>
       </c>
       <c r="AO25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP25" t="n">
         <v>22</v>
@@ -4967,16 +5034,16 @@
         <v>1</v>
       </c>
       <c r="AR25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT25" t="n">
         <v>17</v>
       </c>
-      <c r="AS25" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>18</v>
-      </c>
       <c r="AU25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV25" t="n">
         <v>24</v>
@@ -4994,7 +5061,7 @@
         <v>26</v>
       </c>
       <c r="BA25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB25" t="n">
         <v>4</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -5029,88 +5096,88 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F26" t="n">
         <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>0.784</v>
+        <v>0.778</v>
       </c>
       <c r="H26" t="n">
         <v>48.7</v>
       </c>
       <c r="I26" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="J26" t="n">
-        <v>86.7</v>
+        <v>87</v>
       </c>
       <c r="K26" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L26" t="n">
         <v>10.2</v>
       </c>
       <c r="M26" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="N26" t="n">
         <v>0.376</v>
       </c>
       <c r="O26" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="P26" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.792</v>
+        <v>0.791</v>
       </c>
       <c r="R26" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S26" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="T26" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
       <c r="U26" t="n">
         <v>22.8</v>
       </c>
       <c r="V26" t="n">
-        <v>14.1</v>
+        <v>13.9</v>
       </c>
       <c r="W26" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X26" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AB26" t="n">
-        <v>103.7</v>
+        <v>103.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF26" t="n">
         <v>2</v>
@@ -5119,13 +5186,13 @@
         <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI26" t="n">
         <v>6</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK26" t="n">
         <v>17</v>
@@ -5134,7 +5201,7 @@
         <v>3</v>
       </c>
       <c r="AM26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN26" t="n">
         <v>5</v>
@@ -5167,13 +5234,13 @@
         <v>25</v>
       </c>
       <c r="AX26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA26" t="n">
         <v>25</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -5289,13 +5356,13 @@
         <v>-2</v>
       </c>
       <c r="AD27" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE27" t="n">
         <v>19</v>
       </c>
       <c r="AF27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG27" t="n">
         <v>19</v>
@@ -5304,13 +5371,13 @@
         <v>5</v>
       </c>
       <c r="AI27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ27" t="n">
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL27" t="n">
         <v>29</v>
@@ -5319,7 +5386,7 @@
         <v>28</v>
       </c>
       <c r="AN27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5328,10 +5395,10 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS27" t="n">
         <v>7</v>
@@ -5346,7 +5413,7 @@
         <v>27</v>
       </c>
       <c r="AW27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX27" t="n">
         <v>26</v>
@@ -5361,7 +5428,7 @@
         <v>1</v>
       </c>
       <c r="BB27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC27" t="n">
         <v>20</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -5408,70 +5475,70 @@
         <v>49.2</v>
       </c>
       <c r="I28" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="J28" t="n">
-        <v>82.8</v>
+        <v>82.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0.465</v>
+        <v>0.466</v>
       </c>
       <c r="L28" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.371</v>
+        <v>0.375</v>
       </c>
       <c r="O28" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P28" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>34.1</v>
+        <v>33.9</v>
       </c>
       <c r="T28" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U28" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="V28" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="W28" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X28" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>102.3</v>
+        <v>102.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
         <v>11</v>
@@ -5489,7 +5556,7 @@
         <v>11</v>
       </c>
       <c r="AJ28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
         <v>6</v>
@@ -5507,10 +5574,10 @@
         <v>17</v>
       </c>
       <c r="AP28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR28" t="n">
         <v>25</v>
@@ -5519,19 +5586,19 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AW28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AX28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY28" t="n">
         <v>10</v>
@@ -5540,10 +5607,10 @@
         <v>9</v>
       </c>
       <c r="BA28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BC28" t="n">
         <v>8</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F29" t="n">
         <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>0.694</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="H29" t="n">
         <v>48.6</v>
@@ -5593,52 +5660,52 @@
         <v>39.2</v>
       </c>
       <c r="J29" t="n">
-        <v>85.3</v>
+        <v>85.2</v>
       </c>
       <c r="K29" t="n">
         <v>0.46</v>
       </c>
       <c r="L29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="M29" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.364</v>
+        <v>0.362</v>
       </c>
       <c r="O29" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="P29" t="n">
-        <v>25.6</v>
+        <v>25.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.784</v>
+        <v>0.785</v>
       </c>
       <c r="R29" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S29" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T29" t="n">
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
       <c r="U29" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V29" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="W29" t="n">
         <v>7.3</v>
       </c>
       <c r="X29" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z29" t="n">
         <v>21.8</v>
@@ -5650,19 +5717,19 @@
         <v>107.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AD29" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AE29" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AF29" t="n">
         <v>4</v>
       </c>
       <c r="AG29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AH29" t="n">
         <v>9</v>
@@ -5671,10 +5738,10 @@
         <v>5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL29" t="n">
         <v>8</v>
@@ -5683,22 +5750,22 @@
         <v>7</v>
       </c>
       <c r="AN29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO29" t="n">
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AQ29" t="n">
         <v>3</v>
       </c>
       <c r="AR29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AS29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT29" t="n">
         <v>22</v>
@@ -5713,13 +5780,13 @@
         <v>19</v>
       </c>
       <c r="AX29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AY29" t="n">
         <v>20</v>
       </c>
       <c r="AZ29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA29" t="n">
         <v>4</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -5757,52 +5824,52 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E30" t="n">
         <v>13</v>
       </c>
       <c r="F30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G30" t="n">
-        <v>0.342</v>
+        <v>0.351</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>35.7</v>
+        <v>35.9</v>
       </c>
       <c r="J30" t="n">
-        <v>78.59999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="L30" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M30" t="n">
         <v>20.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0.333</v>
+        <v>0.334</v>
       </c>
       <c r="O30" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P30" t="n">
         <v>23.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.748</v>
+        <v>0.744</v>
       </c>
       <c r="R30" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S30" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T30" t="n">
         <v>42.4</v>
@@ -5811,10 +5878,10 @@
         <v>20.2</v>
       </c>
       <c r="V30" t="n">
-        <v>15.2</v>
+        <v>14.7</v>
       </c>
       <c r="W30" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="X30" t="n">
         <v>5.8</v>
@@ -5823,16 +5890,16 @@
         <v>4.6</v>
       </c>
       <c r="Z30" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AA30" t="n">
         <v>19.9</v>
       </c>
       <c r="AB30" t="n">
-        <v>96</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>-3.1</v>
+        <v>-2.8</v>
       </c>
       <c r="AD30" t="n">
         <v>7</v>
@@ -5841,10 +5908,10 @@
         <v>23</v>
       </c>
       <c r="AF30" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AG30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH30" t="n">
         <v>29</v>
@@ -5862,7 +5929,7 @@
         <v>23</v>
       </c>
       <c r="AM30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN30" t="n">
         <v>24</v>
@@ -5874,28 +5941,28 @@
         <v>13</v>
       </c>
       <c r="AQ30" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT30" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AU30" t="n">
         <v>24</v>
       </c>
       <c r="AV30" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AW30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY30" t="n">
         <v>11</v>
@@ -5904,13 +5971,13 @@
         <v>5</v>
       </c>
       <c r="BA30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
@@ -6017,10 +6084,10 @@
         <v>2.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF31" t="n">
         <v>4</v>
@@ -6035,10 +6102,10 @@
         <v>7</v>
       </c>
       <c r="AJ31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL31" t="n">
         <v>26</v>
@@ -6053,16 +6120,16 @@
         <v>25</v>
       </c>
       <c r="AP31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR31" t="n">
         <v>19</v>
       </c>
       <c r="AS31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT31" t="n">
         <v>15</v>
@@ -6086,7 +6153,7 @@
         <v>19</v>
       </c>
       <c r="BA31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB31" t="n">
         <v>18</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-10-2014-15</t>
+          <t>2015-01-10</t>
         </is>
       </c>
     </row>
